--- a/employees.xlsx
+++ b/employees.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sofia/Desktop/Dynamacs/מנדלסון/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sofia/PycharmProjects/Mendelson/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F7EBBF-F222-5C48-9394-666C99D1D21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E49F08-8E88-9442-AD83-DA6E4D804647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{76B1A70E-36C2-9E4B-B9BC-6E6D070680C3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>שם מלא</t>
   </si>
@@ -33,15 +33,6 @@
     <t>ליקוט</t>
   </si>
   <si>
-    <t xml:space="preserve">רענון </t>
-  </si>
-  <si>
-    <t xml:space="preserve">תפקיד </t>
-  </si>
-  <si>
-    <t>כלי שינוע</t>
-  </si>
-  <si>
     <t>משה אגרה</t>
   </si>
   <si>
@@ -84,23 +75,23 @@
     <t>היגש</t>
   </si>
   <si>
-    <t xml:space="preserve">מלקטת </t>
-  </si>
-  <si>
-    <t>מלגזת היגש</t>
-  </si>
-  <si>
     <t xml:space="preserve">זמן </t>
   </si>
   <si>
-    <t>ליקוט גובה</t>
+    <t>גובה</t>
+  </si>
+  <si>
+    <t>תפקיד</t>
+  </si>
+  <si>
+    <t>רענון</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -116,12 +107,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -182,7 +167,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -193,11 +177,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -513,309 +500,266 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA47D2D1-C530-894D-89EF-E9CDCD152A5D}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="6.1640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="7.1640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="6">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="6">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="7">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="7">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2</v>
+      </c>
+      <c r="E10" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>9</v>
+      </c>
+      <c r="E11" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7">
+        <v>9</v>
+      </c>
+      <c r="E12" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="7">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="7">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="E13" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7">
+        <v>3</v>
+      </c>
+      <c r="E14" s="11">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="7">
-        <v>7</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7">
-        <v>7</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="7">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="8">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="8">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2</v>
-      </c>
-      <c r="F10" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
-        <v>9</v>
-      </c>
-      <c r="F11" s="8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8">
-        <v>9</v>
-      </c>
-      <c r="F12" s="8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3</v>
-      </c>
-      <c r="F14" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="4"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
